--- a/案例库.xlsx
+++ b/案例库.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\大创\cars\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630"/>
+    <workbookView windowWidth="12800" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>TikTok欧盟用户数据跨境传输处罚案</t>
   </si>
@@ -41,6 +46,27 @@
   </si>
   <si>
     <t>Uber跨境数据传输GDPR处罚案</t>
+  </si>
+  <si>
+    <t>迪奥公司被罚案</t>
+  </si>
+  <si>
+    <t>Yango遭受欧盟重处罚案</t>
+  </si>
+  <si>
+    <t>地域</t>
+  </si>
+  <si>
+    <t>欧盟——中国</t>
+  </si>
+  <si>
+    <t>欧盟——美国</t>
+  </si>
+  <si>
+    <t>中国——中国</t>
+  </si>
+  <si>
+    <t>欧盟——俄罗斯</t>
   </si>
   <si>
     <t>案件基本信息</t>
@@ -1198,13 +1224,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="50.6363636363636" defaultRowHeight="30" customHeight="1" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="50.6363636363636" defaultRowHeight="30" customHeight="1" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="16384" width="50.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:5">
+    <row r="1" customHeight="1" spans="1:7">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1217,107 +1243,136 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:5">
+    <row r="2" customHeight="1" spans="1:7">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
+    <row r="3" customHeight="1" spans="1:7">
+      <c r="A3" t="s">
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
+    <row r="4" customHeight="1" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
+    <row r="5" customHeight="1" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
+    <row r="6" customHeight="1" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>29</v>
+    <row r="7" customHeight="1" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
